--- a/basedatos_partidas/salida/descompuestos/12.12.01.060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/12.12.01.060.xlsx
@@ -558,10 +558,10 @@
         <v>0.06</v>
       </c>
       <c r="G10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="13">
@@ -743,7 +743,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="H21" t="n">
         <v>0.02</v>
@@ -762,7 +762,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
     </row>
   </sheetData>
